--- a/IITA climate publications - UPDATED.xlsx
+++ b/IITA climate publications - UPDATED.xlsx
@@ -8377,13 +8377,13 @@
         <v>Backed by Gates Foundation and Stress Tolerant Maize for Africa (STMA) initiative. Data available via IITA CKAN repository.</v>
       </c>
       <c r="T89" t="str">
-        <v/>
+        <v>10.3389/fsufs.2023.1238776</v>
       </c>
       <c r="U89" t="str">
-        <v/>
+        <v>In West and Central Africa (WCA), drought and low soil nitrogen (low N) impede increased maize (Zea mays L.) productivity and production. Due to climate change, the two stresses usually occur together, leading to food, nutritional, and economic insecurity in the sub-region. Moderate to high estimates of heritability were observed for most of the measured traits under stress conditions, indicating that the traits could be easily transmitted to the progenies. Fifty-seven out of the 96 QPM inbreds evaluated exhibited varying degrees of resilience to drought and low N.</v>
       </c>
       <c r="V89" t="str">
-        <v/>
+        <v>climate change, drought, indirect selection for high yield, low soil nitrogen, quality protein maize, stress resilient maize</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -8469,13 +8469,13 @@
         <v>Funded by USAID and CGIAR Roots, Tubers and Bananas (RTB). Highlights knowledge gaps in pathogen-host dynamics and need for multi-environment resistance screening protocols.</v>
       </c>
       <c r="T90" t="str">
-        <v/>
+        <v>10.1111/ppa.12824</v>
       </c>
       <c r="U90" t="str">
-        <v/>
+        <v>Banana and plantain (Musa spp.) are important food crops in tropical and subtropical regions of the world where they generate millions of dollars annually to both subsistence farmers and exporters. Since 1902, Pseudocercospora banana pathogens, Pseudocercospora fijiensis, P. musae and P. eumusae, have emerged as major production constraints to banana and plantain. Despite concerted efforts to counter these pathogens, they have continued to negatively impact banana yield. In this review, the economic importance, distribution and the interactions between Pseudocercospora banana pathogens and Musa species are discussed. Interactions are further scrutinized in the light of an emerging climate change scenario and efforts towards the development of resistant banana germplasm are discussed.</v>
       </c>
       <c r="V90" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -8553,13 +8553,13 @@
         <v>First national study assessing small grain mycotoxin risks in Zimbabwe. Supports regional policy reforms for grain safety and storage.</v>
       </c>
       <c r="T91" t="str">
-        <v/>
+        <v>10.3390/foods10020287</v>
       </c>
       <c r="U91" t="str">
-        <v/>
+        <v>Maize and three small grain cereals (sorghum, pearl millet, and finger millet) produced by smallholder farmers in Zimbabwe during 2016 and 2017 were examined for fungal community structure, and total aflatoxin (AF) and fumonisin (FM) content. A total of 800 maize and 180 small grain samples were collected at harvest and during storage from four agroecological zones. Fusarium spp. dominated the fungi associated with maize. Across crops, Aspergillus flavus constituted the main Aspergillus spp. Small grain cereals were less susceptible to both AF and FM. AF (52%) and FM (89%) prevalence was higher in maize than in small grains (13–25% for AF and 0–32% for FM). Less than 2% of small grain samples exceeded the EU regulatory limit for AF (4 µg/kg), while &lt;10% exceeded the EU regulatory limit for FM (1000 µg/kg).</v>
       </c>
       <c r="V91" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -8633,13 +8633,13 @@
         <v>Supports selection and development of drought- and heat-tolerant cowpea varieties suited to low-input environments in West Africa.</v>
       </c>
       <c r="T92" t="str">
-        <v/>
+        <v>10.25081/jpsp.2022.v8.7896</v>
       </c>
       <c r="U92" t="str">
-        <v/>
+        <v>The study investigated the morpho-physiological responses of two cowpea varieties (IT89KD-288 and IT99K573-1-1) to a combination of stresses (water deficit stress and high light intensity) at different growth stages. Exposure to W4 under L1 considerably reduced cowpea yield by 80% compared to those grown under L3 and full watering. Reduced light intensity enhanced cowpea grain yield irrespective of water deficit stress and IT89KD-288 was superior to IT99K573-1-1. In conclusion, reduced light intensity enhanced cowpea tolerance to water deficit and increased yield. Cowpea response was dependent on growth stage, variety and severity of stress.</v>
       </c>
       <c r="V92" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -8709,13 +8709,13 @@
         <v>Highlights ideational power in shaping resistance to gender policy in climate adaptation; relevant to broader gender policy efforts beyond Uganda.</v>
       </c>
       <c r="T93" t="str">
-        <v/>
+        <v>10.1111/dpr.12458</v>
       </c>
       <c r="U93" t="str">
-        <v/>
+        <v>Expectations that gender-mainstreaming efforts would effectively advance gender equality have been disappointed in contemporary sub-Saharan Africa. Examining this apparent disconnect, we focus on the narratives through which policy-makers relate to, and dis/engage with, gender issues. The research found that narrative shifts exercise four distinct power effects: They (1) shift blame for ineffective gender implementation; (2) legitimize policy inaction; (3) foreground and naturalize patriarchy; and (4) promote the diversion of resources.</v>
       </c>
       <c r="V93" t="str">
-        <v/>
+        <v>Africa, climate change, gender mainstreaming, ideational power, policy narrative, Uganda</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -8788,13 +8788,13 @@
         <v>Part of CGIAR Climate Change, Agriculture and Food Security (CCAFS) and Forest, Trees and Agroforestry (FTA) programs.</v>
       </c>
       <c r="T94" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2020.102812</v>
       </c>
       <c r="U94" t="str">
-        <v/>
+        <v>Improving management practices of cocoa (Theobroma cacao L.) cultivation especially under future climate change requires knowledge of yield gaps and their determining factors. The study assessed yield gaps and their determining factors through multiple regression modelling in smallholder cocoa agroforestry systems in Ghana along a climatic gradient. The studied zones referred to as dry, mid and wet with annual rainfall of 1200, 1200–1400 and 1400–2000 mm respectively. High relative yield gap in dry zone due to low intensification and climatic risk. Labour and available P significantly determined yield gap in the dry and mid zones. Access to trainings and use of hybrid seeds reduced yield gaps in the wet zone.</v>
       </c>
       <c r="V94" t="str">
-        <v/>
+        <v>theobroma cacao; yield gap; yield factors; climate change; smallholders; intensification</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -8872,13 +8872,13 @@
         <v>Religious and spiritual beliefs influence climate perceptions. Radio/TV is the main source of climate info. The study suggests scaling up institutional support to enhance resilience.</v>
       </c>
       <c r="T95" t="str">
-        <v/>
+        <v>10.3390/su14052847</v>
       </c>
       <c r="U95" t="str">
-        <v/>
+        <v>Sahelian countries, particularly Niger, are more vulnerable to climate change due to the high dependence of most of their populations on rain-fed agriculture and limited capacities to respond to climate variability and change. This paper examines the factors influencing climate change adaptation strategies and the impacts on household income and food security in rural Niger. The results showed that crop diversification (72.74%), income diversification (67.97%) and changing planting times (55%) are the main adaptation strategies adopted by households. The majority of respondents had noticed changes in rain patterns (93.21%), in the amount of rain (91.25%) and in the intensity of rain (81.82%) during the last five years.</v>
       </c>
       <c r="V95" t="str">
-        <v/>
+        <v>adaptation strategies; climate change; households; logit regression; matching techniques</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -8956,13 +8956,13 @@
         <v>Stresses need for integrated, tailored adaptation packages and policies that consider inequality. Highlights the role of livestock as coping assets and the limitations of self-reliance in the face of compound shocks.</v>
       </c>
       <c r="T96" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2017.02.006</v>
       </c>
       <c r="U96" t="str">
-        <v/>
+        <v>This paper provides an ex-ante assessment of the impacts of climate and price variability on household income and food security in Ethiopia and Ghana. The study applies an agent-based modelling approach to highlight the role of coping and adaptation strategies under climate and price variability. Our simulation results show that climate and price variability adversely affects income and food security of households in both countries. Self-coping mechanisms are found to be important but insufficient to mitigate the adverse effects of variability, implying the need for policy interventions. Adaptation strategies composed of a portfolio of actions such as the provision of production credit and access to improved seeds are found to be effective in reducing the impacts of climate and price variability in Ethiopia.</v>
       </c>
       <c r="V96" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -9054,13 +9054,13 @@
 Strong connection to farmer memory recall and context-specific responses to climate threats</v>
       </c>
       <c r="T97" t="str">
-        <v/>
+        <v>10.1007/s10113-012-0351-0</v>
       </c>
       <c r="U97" t="str">
-        <v/>
+        <v>The savanna region of Africa is a potential breadbasket of the continent but is severely affected by climate change. Understanding farmers' perceptions of climate change and the types of adjustments they have made in their farming practices in response to these changes will offer some insights into necessary interventions to ensure a successful adaptation in the region. This paper explores how smallholder farmers in the Nigerian savanna perceive and adapt to climate change. The results show that most of the farmers have noticed changes in climate and have consequently adjusted their farming practices to adapt. There are no large differences in the adaptation practices across the region, but farmers in Sudan savanna agro-ecological zone are more likely to adapt to changes in temperature than those in northern Guinea savanna.</v>
       </c>
       <c r="V97" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="98" xml:space="preserve">
@@ -9140,13 +9140,13 @@
 Grounded in national policy relevance (SDGs 1, 2, and 13)</v>
       </c>
       <c r="T98" t="str">
-        <v/>
+        <v>10.1016/j.jclepro.2018.06.221</v>
       </c>
       <c r="U98" t="str">
-        <v/>
+        <v>The paper explores the nexus of rainfall variability and food poverty, which is important for appropriate understanding of the temporal and spatial conditions of the situation, and for policy intervention for Nigeria, which is Africa's most populous and largest economy. The study focuses on Nigeria's agrarian economy which is largely rain-fed, noting that changes in the mean and variability of rainfall affect the hydrological cycle (onset and cessation) of rainfall, with significant effects on rain-fed agricultural and food production systems, and that variability in rainfall can be expected to intensify the cycle of poverty in an agrarian economy like Nigeria.</v>
       </c>
       <c r="V98" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
@@ -9238,13 +9238,13 @@
 Emphasizes value of African breeding programs using IITA germplasm in drought-prone zones.</v>
       </c>
       <c r="T99" t="str">
-        <v/>
+        <v>10.3389/fphys.2013.00093</v>
       </c>
       <c r="U99" t="str">
-        <v/>
+        <v>Cassava is an important crop in Africa, Asia, Latin America, and the Caribbean. Cassava can be produced adequately in drought conditions making it the ideal food security crop in marginal environments. Although cassava can tolerate drought stress, it can be genetically improved to enhance productivity in such environments. Drought adaptation studies in over three decades in cassava have identified relevant mechanisms which have been explored in conventional breeding. This paper highlights some modified traits suitable for early-growth phase phenotyping that may be used to reduce drought phenotyping cycle in cassava. The need for metabolite profiling, improved phenomics to take advantage of next generation sequencing technologies and high throughput phenotyping are basic steps for future direction to improve genetic gain and maximize speed for drought tolerance breeding.</v>
       </c>
       <c r="V99" t="str">
-        <v/>
+        <v>adaptation; drought tolerance; modern breeding; phenotyping; storage roots</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -9328,13 +9328,13 @@
 A rare example of interdisciplinary agenda-setting within agricultural science.</v>
       </c>
       <c r="T100" t="str">
-        <v/>
+        <v>10.1111/wre.12304</v>
       </c>
       <c r="U100" t="str">
-        <v/>
+        <v>Weedy plants pose a major threat to food security, biodiversity, ecosystem services and consequently to human health and wellbeing. However, many currently used weed management approaches are increasingly unsustainable. To address this knowledge and practice gap, in June 2014, 35 weed and invasion ecologists, weed scientists, evolutionary biologists and social scientists convened a workshop to explore current and future perspectives and approaches in weed ecology and management. A horizon scanning exercise ranked a list of 124 pre-submitted questions to identify a priority list of 30 questions.</v>
       </c>
       <c r="V100" t="str">
-        <v/>
+        <v>agroecology; integrated weed management; invasive plants; transdisciplinary research; weed adaptation</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -9418,13 +9418,13 @@
 Supports use of ex-ante modeling for climate-resilient agricultural investments</v>
       </c>
       <c r="T101" t="str">
-        <v/>
+        <v>10.1016/j.gfs.2016.08.003</v>
       </c>
       <c r="U101" t="str">
-        <v/>
+        <v>Achieving and maintaining global food security is challenged by changes in population, income, and climate, among other drivers. Assessing these threats and weighing possible solutions requires a robust multidisciplinary approach. The paper uses the IMPACT system of models to run alternative scenarios for drought and heat tolerant crop varieties under two extreme future climate scenarios. Detailed, location-specific data on climate, soil type, and physiological crop parameters are incorporated into the DSSAT crop models. The structural approach captures key knowledge across multiple areas of expertise. Economic responses reduce yield shocks from crop models. Drought and heat tolerant crops improve productivity with or without climate change.</v>
       </c>
       <c r="V101" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="102" xml:space="preserve">
@@ -9510,13 +9510,13 @@
 Recommends integrating indigenous knowledge with scientific forecasts for better targeting of adaptation policies</v>
       </c>
       <c r="T102" t="str">
-        <v/>
+        <v>10.1080/17565529.2017.1374236</v>
       </c>
       <c r="U102" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
       <c r="V102" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="103" xml:space="preserve">
@@ -9606,13 +9606,13 @@
 Suggests that adaptation will require moving coffee production upslope, which may threaten biodiversity conservation areas.</v>
       </c>
       <c r="T103" t="str">
-        <v/>
+        <v>10.1016/j.agrformet.2015.03.005</v>
       </c>
       <c r="U103" t="str">
-        <v/>
+        <v>Coffee is the world's most valuable tropical export crop. Recent studies predict severe climate change impacts on Coffea arabica (C. arabica) production. However, quantitative production figures are necessary to provide coffee stakeholders and policy makers with evidence to justify immediate action. Using data from the northern Tanzanian highlands, we demonstrate for the first time that increasing night time (Tmin) temperature is the most significant climatic variable responsible for diminishing C. arabica yields between 1961 and 2012. Projecting this forward, every 1 °C rise in Tmin will result in annual yield losses of 137 ± 16.87 kg ha−1. According to our ARIMA model, average coffee production will drop to 145 ± 41 kg ha−1 by 2060. Consequently, without adequate adaptation strategies and/or substantial external inputs, coffee production will be severely reduced in the Tanzanian highlands in the near future.</v>
       </c>
       <c r="V103" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="104" xml:space="preserve">
@@ -9692,13 +9692,13 @@
         <v>Supports climate-smart decision-making for sorghum intensification. Combines APSIM modeling, field trials, and policy relevance. Funded through CGIAR and TAMASA initiative.</v>
       </c>
       <c r="T104" t="str">
-        <v/>
+        <v>10.3390/agronomy13030727</v>
       </c>
       <c r="U104" t="str">
-        <v/>
+        <v>In the context of climate change, the sowing date and cultivar choice can influence the productivity of sorghum, especially where production is constrained by low soil fertility and early terminal drought across the challenging agro-ecologies of north-eastern Nigeria. The APSIM crop model was calibrated and validated to simulate the growth and yield of sorghum cultivars with differing maturing periods sown within varying planting time windows under improved agricultural practices. The seasonal climate simulations across sites and AEZs suggested increased yields when using adapted sorghum cultivars based on the average grain yield threshold of ≥1500 kgha−1. The optimal PWs ranged from 25 May to 30 June for some cultivars while the PWs could be extended to 10 July for others.</v>
       </c>
       <c r="V104" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="105" xml:space="preserve">
@@ -9780,13 +9780,13 @@
 Highlights role of human-induced disturbance in driving rapid forest composition shifts</v>
       </c>
       <c r="T105" t="str">
-        <v/>
+        <v>10.1038/s41586-021-03483-6</v>
       </c>
       <c r="U105" t="str">
-        <v/>
+        <v>Africa is forecasted to experience large and rapid climate change and population growth during the twenty-first century, which threatens the world's second largest rainforest. Protecting and sustainably managing these African forests requires an increased understanding of their compositional heterogeneity, the environmental drivers of forest composition and their vulnerability to ongoing changes. The study uses a dataset of 6 million trees in more than 180,000 field plots to jointly model the distribution in abundance of the most dominant tree taxa in central Africa, producing continuous maps of the floristic and functional composition of central African forests. The results show that the uncertainty in taxon-specific distributions averages out at the community level, and reveal highly deterministic assemblages.</v>
       </c>
       <c r="V105" t="str">
-        <v/>
+        <v>Climate-change impacts; Community ecology; Forest ecology; Tropical ecology; Floristic composition of forest; Functional composition of forest; Soil types; Anthropogenic gradients; African rainforest</v>
       </c>
     </row>
     <row r="106" xml:space="preserve">
@@ -9878,13 +9878,13 @@
 The project linked closely with Africa RISINGâ€™s technology park and on-farm trials</v>
       </c>
       <c r="T106" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
       <c r="U106" t="str">
-        <v/>
+        <v>Smallholder farmers in Northern Ghana regularly face shocks, challenging the sustainability of their farms and livelihoods. Different farm households and household members may be differently affected and respond with different coping strategies. We combined whole-farm modelling and farmer consultations to investigate the vulnerability, buffer and adaptive capacity of three farm types in Northern Ghana towards severe climate, economic and social shocks. Our model results indicate that the drought shock would most severely affect all farm types, drastically reducing their operating profits and soil organic matter balance.</v>
       </c>
       <c r="V106" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="107" xml:space="preserve">
@@ -9966,13 +9966,13 @@
 Highlights relevance for informing early warning, planning, and climate adaptation priorities in vulnerable Sahelian states</v>
       </c>
       <c r="T107" t="str">
-        <v/>
+        <v>10.1080/01431161.2023.2234094</v>
       </c>
       <c r="U107" t="str">
-        <v/>
+        <v>Agricultural drought is a complex phenomenon with numerous consequences and negative implications for agriculture and food systems. The Sahel is frequently affected by severe droughts, leading to significant losses in agricultural yields. The study develops a new multivariate agricultural drought vulnerability index (MADVI) that combines static and dynamic factors extracted from satellite data. The results showed statistical agreement between the predicted MADVI spatial variability and the reference model (R=0.86 for RF). The overall vulnerability situation in the watershed is 21.8% extreme, 10% very high, 16.8% high, 27.7% moderate, 22.2% low and 1.5% relatively low.</v>
       </c>
       <c r="V107" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -10060,13 +10060,13 @@
 IITAâ€™s support of this research underlines its focus on resilience and sustainable development in smallholder agriculture in Sub-Saharan Africa.</v>
       </c>
       <c r="T108" t="str">
-        <v/>
+        <v>10.3390/su16135766</v>
       </c>
       <c r="U108" t="str">
-        <v/>
+        <v>Smallholder farmers in Ethiopia face increasing challenges from climate change and variability, which threaten their food security and livelihoods. The study focuses on how climate change adaptation strategies impact household vulnerability to food insecurity in Southwest Ethiopia.</v>
       </c>
       <c r="V108" t="str">
-        <v/>
+        <v>climate change adaptation; food insecurity; vulnerability; multinomial endogenous treatment effect; smallholder farmers; Ethiopia</v>
       </c>
     </row>
     <row r="109" xml:space="preserve">
@@ -10134,13 +10134,13 @@
         <v>Suggests spatial self-organization may be useful for resilience monitoring, but transient effects mean these systems need long-term observation and caution in interpretation.</v>
       </c>
       <c r="T109" t="str">
-        <v/>
+        <v>10.1111/ecog.06139</v>
       </c>
       <c r="U109" t="str">
-        <v/>
+        <v>Regular vegetation patterns have been predicted to indicate a system slowing down and possibly desertification of drylands. However, these predictions have not yet been observed in dryland vegetation due to the inherent logistic difficulty to gather longer-term in situ data. Here, we evaluate the theoretical prediction that regular vegetation patterns are associated with empirically derived temporal indicators of critical slowing down in a dryland ecosystem in Sudan using different remote sensing products. Overall, three temporal indicators show slowing down as vegetation patterns change from gaps to labyrinths to spots towards more arid conditions. Our findings suggest that spatial self-organization of dryland vegetation is associated with critical slowing down, but this transition towards reduced resilience happens in a non-linear way.</v>
       </c>
       <c r="V109" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="110" xml:space="preserve">
@@ -10234,13 +10234,13 @@
 Emphasizes integrated approaches across institutions, geographies, and farming systems</v>
       </c>
       <c r="T110" t="str">
-        <v/>
+        <v>10.1016/j.wace.2014.04.004</v>
       </c>
       <c r="U110" t="str">
-        <v/>
+        <v>Agriculture and the economies of Sub-Saharan Africa (SSA) are highly sensitive to climatic variability. Drought, in particular, represents one of the most important natural factors contributing to malnutrition and famine in many parts of the region. This paper attempts to highlight the challenges of drought in SSA and reviews the current drought risk management strategies, especially the promising technological and policy options for managing drought risks to protect livelihoods and reduce vulnerability. The review suggests the possibilities of several ex ante and ex post drought management strategies in SSA although their effectiveness depends on agro-climatic and socio-economic conditions. A proactive approach that combines promising technological, institutional and policy solutions to manage the risks within vulnerable communities is considered to be the way forward.</v>
       </c>
       <c r="V110" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="111" xml:space="preserve">
@@ -10424,13 +10424,13 @@
 Recognizes IITAâ€™s role via CoFCCA in linking rural institutions with regional adaptation knowledge.</v>
       </c>
       <c r="T112" t="str">
-        <v/>
+        <v>10.1080/17565529.2017.1291409</v>
       </c>
       <c r="U112" t="str">
-        <v/>
+        <v>Climate change will create challenges for forest-dependent communities in Africa. Local institutions play an important role in fostering community resilience in the context of change. The resilience of a community is influenced by social learning that can happen as people meet together and share their diverse experiences and knowledge. Surveys of 232 people from 13 villages, in three regions of Cameroon, provided insight about the role that internal village institutions can play in fostering community resilience. Almost all villagers, both men and women, are members of at least one group and the membership of these groups is very diverse in terms of family relations, gender, occupation, age, and level of education. While the groups were not currently working together to respond to climate change, the diverse social networks that villagers have in these groups have already fostered exchange of knowledge. Community resilience could be better fostered through a deliberate action-reflection process that includes both men and women, and builds on the social capital present in communities.</v>
       </c>
       <c r="V112" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="113" xml:space="preserve">
@@ -10506,13 +10506,13 @@
         <v>Supports Africa RISING and CGIAR resilience-building strategies. Uses robust econometrics to distinguish indirect vs. interaction effects.</v>
       </c>
       <c r="T113" t="str">
-        <v/>
+        <v>10.1016/j.ecolecon.2023.107894</v>
       </c>
       <c r="U113" t="str">
-        <v/>
+        <v>This paper examines how resilience capacity mediates or moderates the relationship between weather shocks and household food security based on two waves of farm household survey and satellite-based weather data in northern Ghana and applying econometric models. Results show that resilience capacity moderate or mediates the negative effects of heat stress and drought on food security. However, the mediating role of resilience capacity in the shock-food security nexus is more stable and stronger than its moderating role. A standard deviation (SD) increase in heat stress reduces household food consumption by 0.71 SD, but resilience capacity effectively moderates this effect by approximately 0.61 SD. For drought, household food consumption is reduced by 0.67 SD, but resilience capacity effectively dampens this negative effect by approximately 0.60 SD.</v>
       </c>
       <c r="V113" t="str">
-        <v/>
+        <v>Correlated random effects, Food security, Weather shocks, Resilience capacity, Ghana</v>
       </c>
     </row>
     <row r="114" xml:space="preserve">
@@ -10594,13 +10594,13 @@
         <v>Supports national REDD+ strategies; provides policy recommendations for farmer support systems and tenure security to enable CSA adoption.</v>
       </c>
       <c r="T114" t="str">
-        <v/>
+        <v>10.3390/land7010030</v>
       </c>
       <c r="U114" t="str">
-        <v/>
+        <v>Agriculture in Africa is not only exposed to climate change impacts but is also a source of greenhouse gases (GHGs). While GHG emissions in Africa are relatively minimal in global dimensions, agriculture in the continent constitutes a major source of GHG emissions. In Ghana, agricultural emissions are accelerating, mainly due to ensuing deforestation of which smallholder cocoa farming is largely associated. The sector is also bedevilled by soil degradation, pests, diseases and poor yields coupled with poor agronomic practices. Climate Smart Agriculture (CSA) thus offers a way to reduce the sector's GHG emissions and to adapt the sector to the adverse impacts of climate change. This study assesses the potential of CSA vis-à-vis conventional cocoa systems to enhance production, mitigate and/or remove GHG emissions and build resilience, in addition to understanding key determinants influencing CSA practices.</v>
       </c>
       <c r="V114" t="str">
-        <v/>
+        <v>climate smart agriculture, resilience, carbon balance, cocoa, mitigation, Ghana, Ex-ACT, agroforestry</v>
       </c>
     </row>
     <row r="115" xml:space="preserve">
@@ -10682,13 +10682,13 @@
         <v>Recommends better infrastructure (roads, rail), finance and insurance tools, and conflict mitigation strategies to protect trader resilience.</v>
       </c>
       <c r="T115" t="str">
-        <v/>
+        <v>10.1108/JADEE-08-2023-0214</v>
       </c>
       <c r="U115" t="str">
-        <v/>
+        <v>The study examines five exogenous shocks: climate, violence, price hikes, spoilage and the COVID-19 lockdown, and analyzes the association between these shocks and trader characteristics, reflecting trader vulnerability. Using primary survey data on 1,100 Nigerian maize traders for 2021 (controlling for shocks in 2017), the researchers use probit models to estimate the probabilities of experiencing climate, violence, disease and cost shocks associated with trader characteristics (gender, size and region) and to estimate the probability of vulnerability (experiencing severe impacts). Traders are prone to experiencing more than one shock, which increases the intensity of the shocks, with price shocks often accompanied by violence, climate and COVID-19 shocks.</v>
       </c>
       <c r="V115" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="116" xml:space="preserve">
@@ -10766,13 +10766,13 @@
         <v>The framework is proposed as a tool for CGIAR and national programs to guide breeding, agronomy, and policy strategies for long-term climate resilience planning.</v>
       </c>
       <c r="T116" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2022.103508</v>
       </c>
       <c r="U116" t="str">
-        <v/>
+        <v>Given the significance of climate change impacts on farming communities, large investments are made by research and development actors to adapt agricultural systems. A data-driven approach is required to guide these investments. In the African Great Lakes Region (GLR), root, tuber and banana (RT&amp;B) crops are vital for smallholder farming systems, but little is known about strategies to mitigate climate change impacts. The objective was to develop a spatial prioritisation and targeting framework based on the risk of climate-related impacts to guide research investments in climate-smart agriculture for RT&amp;B crops in the GLR. The framework is based on crop-specific socio-agroecological homologues (SAHs), defined as clusters of geographies with broadly similar risks of climate-change related impacts, determined by hazard, exposure, and vulnerability. Four SAHs were identified for banana, potato and sweetpotato, and five for cassava. For each crop, SAHs were prioritised for investment based on the level of risk. Scenario analysis showed that drought-tolerant varieties would increase banana suitability from 0.30 to 0.47 under baseline conditions and from 0.54 to 0.71 under future climates.</v>
       </c>
       <c r="V116" t="str">
-        <v/>
+        <v>Climate change adaptation, Root tuber and banana crops, African Great Lakes Region, Spatial prioritisation, Socio-agroecological homologues, Risk assessment, Climate-smart agriculture</v>
       </c>
     </row>
     <row r="117" xml:space="preserve">
@@ -10856,13 +10856,13 @@
 Contributes to empirical data gaps on cocoa heat tolerance</v>
       </c>
       <c r="T117" t="str">
-        <v/>
+        <v>10.1016/j.envexpbot.2022.105052</v>
       </c>
       <c r="U117" t="str">
-        <v/>
+        <v>Shade is one of the recommended management solutions to mitigate the effects of heat stress, which is a major challenge for cocoa production globally. Nevertheless, there are limited studies to verify this hypothesis. The study evaluated the effects of heat and shade on cocoa physiology using experimental plots with six-month old potted seedlings in a randomized complete block design. Infrared heaters were applied for one month to increase leaf temperatures by an average of 5-7°C (heat treatment) compared with no heat (unheated treatments), and shaded plants were placed under a shade net removing 60% of the light compared with no shade (sun treatments). Plants under heat treatments in sun and in shade showed severe reduction in photosynthesis. Measurements of chlorophyll fluorescence and photosynthetic light response curves indicated that heat caused damages at photosystem II and additionally resulted in lower rates of maximal photosynthesis. Heat treatments resulted in decreased concentrations of chlorophyll and changed pigment composition, reduced specific leaf areas, and plant biomass. While shade may benefit cocoa seedlings, the results indicate that the positive effects may not be sufficient to counteract the negative effects of increased temperatures on cocoa physiology.</v>
       </c>
       <c r="V117" t="str">
-        <v/>
+        <v>shade, cocoa (plant), heat, Stomatal conductance, water potential, photosynthesis, ghana</v>
       </c>
     </row>
     <row r="118" xml:space="preserve">
@@ -10944,13 +10944,13 @@
 Data used to guide donor incorporation into breeding pipelines for SSA.</v>
       </c>
       <c r="T118" t="str">
-        <v/>
+        <v>10.2135/cropsci2012.09.0545</v>
       </c>
       <c r="U118" t="str">
-        <v/>
+        <v>Low maize (Zea mays L.) yields and the impacts of climate change on maize production highlight the need to improve yields in eastern and southern Africa. Climate projections suggest higher temperatures within drought-prone areas. Research in model species suggests that tolerance to combined drought and heat stress is genetically distinct from tolerance to either stress alone, but this has not been confirmed in maize. In this study we evaluated 300 maize inbred lines testcrossed to CML539. Experiments were conducted under optimal conditions, reproductive stage drought stress, heat stress, and combined drought and heat stress. Lines with high levels of tolerance to drought and combined drought and heat stress were identified. Significant genotype × trial interaction and very large plot residuals were observed; consequently, the repeatability of individual managed stress trials was low. Tolerance to combined drought and heat stress in maize was genetically distinct from tolerance to individual stresses, and tolerance to either stress alone did not confer tolerance to combined drought and heat stress. This finding has major implications for maize drought breeding. Many current drought donors and key inbreds used in widely-grown African hybrids were susceptible to drought stress at elevated temperatures.</v>
       </c>
       <c r="V118" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="119" xml:space="preserve">
@@ -11034,13 +11034,13 @@
 Suggests targeting of strategies based on household type rather than blanket promotion</v>
       </c>
       <c r="T119" t="str">
-        <v/>
+        <v>10.1007/s10113-015-0838-6</v>
       </c>
       <c r="U119" t="str">
-        <v/>
+        <v>The paper examines adaptation strategies to reduce smallholder farmers' vulnerability to climate variability in West Africa, exploring linkages between agricultural adaptation strategies (crop diversity, soil and water conservation, trees on farm, small ruminants, improved crop varieties, fertilizers), food security, farm household characteristics and farm productivity in three contrasting agro-ecological sites (Burkina Faso, Ghana and Senegal). The study found that differences in land area per capita and land productivity largely explained variation in food security across sites, and distinguished four household types (subsistence, diversified, extensive, intensified) based on land size and market orientation, with contrasting levels of food security and agricultural adaptation strategies.</v>
       </c>
       <c r="V119" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="120" xml:space="preserve">
@@ -11132,13 +11132,13 @@
 Strong emphasis on the need for climate justice and support to smallholders who contribute least to climate change but are most affected.</v>
       </c>
       <c r="T120" t="str">
-        <v/>
+        <v>10.1016/j.cosust.2014.07.002</v>
       </c>
       <c r="U120" t="str">
-        <v/>
+        <v>The 'sustainable intensification' (SI) approach and 'climate-smart agriculture' (CSA) are highly complementary. SI is an essential means of adapting to climate change, also resulting in lower emissions per unit of output. With its emphasis on improving risk management, information flows and local institutions to support adaptive capacity, CSA provides the foundations for incentivizing and enabling intensification. But adaptation requires going beyond a narrow intensification lens to include diversified farming systems, local adaptation planning, building responsive governance systems, enhancing leadership skills, and building asset diversity. While SI and CSA are crucial for global food and nutritional security, they are only part of a multi-pronged approach, that includes reducing consumption and waste, building social safety nets, facilitating trade, and enhancing diets.</v>
       </c>
       <c r="V120" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="121" xml:space="preserve">
@@ -11210,13 +11210,13 @@
         <v>Data collected over 5 years; emphasizes need for conserving submontane forests and promoting less destructive agroforestry practices.</v>
       </c>
       <c r="T121" t="str">
-        <v/>
+        <v>10.1016/j.ecolind.2019.105741</v>
       </c>
       <c r="U121" t="str">
-        <v/>
+        <v>The conservation and sustainable management of biodiversity requires an understanding of the biotic and abiotic factors that condition the presence and survival of organisms in natural habitats. The global distribution and ecological hypersensitivity of pteridophytes have made them ideal candidates for studying the impact of biotic and abiotic factors on levels of biodiversity. This study aims to determine the effect of vegetation cover, human disturbance, and climatic factors on the distribution and diversity of pteridophytes in Togo with a view to guide conservation efforts. Our data comprises 130 plots of 500 m2 representing all ecological zones of the country, complemented by several opportunistic collections. After determining the patterns of pteridophyte distribution, multivariate analysis of variance and the calculation of diversity indicators made it possible to determine the influence of the factors studied. Submontane forests concentrate 90% of the local pteridophyte species in Togo. Humidity, insolation and disturbance are the main drivers of pteridophyte presence. Human disturbances are more damaging to terrestrial pteridophyte species. Pteridophyte species are reliable indicators of conditions of their habitat in Togo.</v>
       </c>
       <c r="V121" t="str">
-        <v/>
+        <v>climate change, vulnerability, protected areas, togo, west africa, biodiversity conservation, nature conservation, pteridophyta</v>
       </c>
     </row>
     <row r="122" xml:space="preserve">
@@ -11294,13 +11294,13 @@
         <v>CBA can mobilize youth and women, as in India, and influence policy reforms. The article argues for procedural justice and long-term institutional embedding of adaptation knowledge rather than one-off projects.</v>
       </c>
       <c r="T122" t="str">
-        <v/>
+        <v>10.1080/17565529.2014.965654</v>
       </c>
       <c r="U122" t="str">
-        <v/>
+        <v>Climate change creates widespread risks for food production. As climate impacts are often locally specific, it is imperative that large-scale initiatives to support smallholder farmers consider local priorities and integrate lessons from successful autonomous adaptation efforts. This article explores how large-scale programmes for smallholder adaptation to climate change might link effectively with community-led adaptation initiatives. Drawing on experiences in Bangladesh, Mozambique, Uganda and India, this article identifies key success factors and barriers for considering local priorities, capacities and lessons in large-scale adaptation programmes. It highlights the key roles of extension services and farmers' organizations as mechanisms for linking between national-level and community-level adaptation, and a range of other success factors which include participative and locally driven vulnerability assessments, tailoring of adaptation technologies to local contexts, mapping local institutions and working in partnership across institutions. Barriers include weak governance, gaps in the regulatory and policy environment, high opportunity costs, low literacy and underdeveloped markets. The article concludes that mainstreaming climate adaptation into large-scale agricultural initiatives requires not only integration of lessons from community-based adaptation, but also the building of inclusive governance to ensure smallholders can engage with those policies and processes affecting their vulnerability.</v>
       </c>
       <c r="V122" t="str">
-        <v/>
+        <v>climate change, community-based adaptation, mainstreaming, agriculture, adaptation</v>
       </c>
     </row>
     <row r="123" xml:space="preserve">
@@ -11378,13 +11378,13 @@
         <v>Significant gap between CSAâ€™s conceptual framework and its operationalization; stresses the need for institutional innovation to complement technical CSA solutions.</v>
       </c>
       <c r="T123" t="str">
-        <v/>
+        <v>10.3390/su10061990</v>
       </c>
       <c r="U123" t="str">
-        <v/>
+        <v>Climate-smart agriculture (CSA) is increasingly seen as a promising approach to feed the growing world population under climate change. The review explored how institutional perspectives are reflected in the CSA literature. In total, 137 publications were analyzed using institutional analysis framework, of which 55.5% make specific reference to institutional dimensions. While the CSA concept encompasses three pillars (productivity, adaptation, and mitigation), the literature has hardly addressed them in an integrated way. Mitigation was predominantly addressed in high-income countries, while productivity and adaptation were priorities for middle and low-income countries.</v>
       </c>
       <c r="V123" t="str">
-        <v/>
+        <v>climate-smart agriculture, institutions, adaptation, mitigation, systematic review</v>
       </c>
     </row>
     <row r="124" xml:space="preserve">
@@ -11478,13 +11478,13 @@
 Focused on research-for-development and donor alignment in CSA inv</v>
       </c>
       <c r="T124" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2018.09.009</v>
       </c>
       <c r="U124" t="str">
-        <v/>
+        <v>Climate-smart agriculture (CSA) is widely promoted as an approach for reorienting agricultural development under the realities of climate change. Prioritising research-for-development activities is crucial, given the need to utilise scarce resources as effectively as possible. However, no framework exists for assessing and comparing different CSA research investments. Several aspects make it challenging to prioritise CSA research, including its multi-dimensional nature (productivity, adaptation and mitigation), the uncertainty surrounding many climate impacts, and the scale and temporal dependencies that may affect the benefits and costs of CSA adoption.</v>
       </c>
       <c r="V124" t="str">
-        <v/>
+        <v>Adaptation, Agriculture, Climate change, Mitigation, Research</v>
       </c>
     </row>
     <row r="125" xml:space="preserve">
@@ -11572,13 +11572,13 @@
 Calls for complementary pest control methods alongside biocontrol</v>
       </c>
       <c r="T125" t="str">
-        <v/>
+        <v>10.1002/ps.6478</v>
       </c>
       <c r="U125" t="str">
-        <v/>
+        <v>The southern armyworm (SAW) Spodoptera eridania (Stoll) (Lepidoptera: Noctuidae) is native to the tropical Americas where the pest can feed on more than 100 plant species. SAW was recently detected in West and Central Africa, feeding on various crops including cassava, cotton, amaranth and tomato. The current work was carried out to predict the potential spatial distribution of SAW and four of its co-evolved parasitoids at a global scale using the maximum entropy (Maxent) algorithm. SAW may not be a huge problem outside its native range (the Americas) for the time being, but may compromise crop yields in specific hotspots in coming years. The analysis of its potential distribution anticipates that the pest might easily migrate east and south from Cameroon and Gabon. The models used generally demonstrate that all the parasitoids considered are good candidates for the biological control of SAW globally, except they will not be able to establish in specific climates. The current paper discusses the potential role of biological control using parasitoids as a crucial component of a durable climate-smart integrated management of SAW to support decision making in Africa and in other regions of bioclimatic suitability.</v>
       </c>
       <c r="V125" t="str">
-        <v/>
+        <v>biological control, climate change, decision support, foresight analysis, southern armyworm</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
@@ -11666,13 +11666,13 @@
 Intended as an actionable strategy, not a research paper.</v>
       </c>
       <c r="T126" t="str">
-        <v/>
+        <v>Note: Published article found is from 2024, not 2022. DOI: 10.3390/su16156652</v>
       </c>
       <c r="U126" t="str">
-        <v/>
+        <v>The paper discusses how the One Health concept has evolved from its initial focus on zoonotic diseases to a broader framework addressing interconnected terrestrial and aquatic ecosystems. The paper describes Climate-Smart One Health (CS-OH) and Climate-Smart Integrated Pest Management (CS-IPM) approaches.</v>
       </c>
       <c r="V126" t="str">
-        <v/>
+        <v>Unable to locate 2022 version; 2024 version published with different DOI</v>
       </c>
     </row>
     <row r="127" xml:space="preserve">
@@ -11760,13 +11760,13 @@
 IITAâ€™s Biorisk Management Facility (BIMAF) acknowledged as key institutional supportâ€‹</v>
       </c>
       <c r="T127" t="str">
-        <v/>
+        <v>10.3390/insects12040273</v>
       </c>
       <c r="U127" t="str">
-        <v/>
+        <v>The fall armyworm (FAW), Spodoptera frugiperda has now become a pest of global importance. Its introduction and detection in Africa in 2016, and subsequent introduction and spread into Asia and Australia, has put several millions of food producers and maize farmers at risk. The present study was initiated to predict the habitats of high establishment potential of key parasitoids of FAW in South America, which might prove to be effective as classical biological control agents of FAW in regions where it is an invasive species under current and future climate scenarios. The prospective parasitoids are the following: Chelonus insularis, Cotesia marginiventris, Eiphosoma laphygmae, Telenomus remus and Trichogramma pretiosum. An adjusted procedure of a machine-learning algorithm, the maximum entropy (Maxent), was applied for the modeling experiments. Model predictions showed particularly high establishment potential of the five hymenopteran parasitoids in areas that are heavily affected by FAW (like the coastal belt of West Africa from Côte d'Ivoire to Nigeria, the Congo basin to Eastern Africa, Eastern, Southern and Southeastern Asia and some portions of Eastern Australia) and those of potential invasion risks (western &amp; southern Europe).</v>
       </c>
       <c r="V127" t="str">
-        <v/>
+        <v>Spodoptera Frugiperda, Climate Change, Pest Management, Biological Control, Machine Learning, Decision Support, Parasitoids</v>
       </c>
     </row>
     <row r="128" xml:space="preserve">
@@ -11858,13 +11858,13 @@
 Clear linkages to IITA-led innovations like the Farmer Interface Application (FIA)</v>
       </c>
       <c r="T128" t="str">
-        <v/>
+        <v>10.1016/j.cois.2022.100961</v>
       </c>
       <c r="U128" t="str">
-        <v/>
+        <v>IPM 3.0 relies on 3 pillars: farmer empowerment, nature-based solutions, integrative practices. It encompasses interactions occurring at cropping system/landscape and across trophic levels. Each year, Africa loses half of its harvest to pests (insects, pathogens, nematodes, weeds). Pest management in major cropping systems has long been dominated by chemical pesticides in Africa. Smallholder farmers have perceived pesticides as insurance to protect their crops. Hence, overuse of pesticides has been constantly increasing. Although African countries have a number of pesticide-related policies, they are inadequately implemented. However, significant investment has been made on integrated pest management (IPM) innovations in recent decades.</v>
       </c>
       <c r="V128" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="129" xml:space="preserve">
@@ -11946,13 +11946,13 @@
 Recommends continued support for digitization of African herbaria and database integration</v>
       </c>
       <c r="T129" t="str">
-        <v/>
+        <v>10.1186/s12915-017-0356-8</v>
       </c>
       <c r="U129" t="str">
-        <v/>
+        <v>Understanding the patterns of biodiversity distribution and what influences them is a fundamental pre-requisite for effective conservation and sustainable utilisation of biodiversity. Such knowledge is increasingly urgent as biodiversity responds to the ongoing effects of global climate change. Nowhere is this more acute than in species-rich tropical Africa, where so little is known about plant diversity and its distribution. In this paper, we use RAINBIO – one of the largest mega-databases of tropical African vascular plant species distributions ever compiled – to address questions about plant and growth form diversity across tropical Africa. The filtered RAINBIO dataset contains 609,776 georeferenced records representing 22,577 species. Growth form data are recorded for 97% of all species.</v>
       </c>
       <c r="V129" t="str">
-        <v/>
+        <v>Botanical exploration, Digitization, Floristic patterns, Herbarium specimens, Plant growth form, Species richness, Tropical forests</v>
       </c>
     </row>
     <row r="130" xml:space="preserve">
@@ -12042,13 +12042,13 @@
 IITA affiliation brings institutional weight to practical policy recommendations</v>
       </c>
       <c r="T130" t="str">
-        <v/>
+        <v>10.3389/fagro.2022.957011</v>
       </c>
       <c r="U130" t="str">
-        <v/>
+        <v>The paper discusses how recent discourse on food sovereignty emphasizes democracy in determining localized food systems and culturally appropriate food while leaning on sustainable agricultural practices such as organic agriculture, ecological intensification, agroecology, nature-based solutions, and regenerative agriculture. Sustainable agricultural practices focus on managing land without synthetic fertilizers and pesticides while improving soil and land health. However, the authors question the practicalities of food activism and relying entirely on nature while yields remain very low in much of sub-Saharan Africa.</v>
       </c>
       <c r="V130" t="str">
-        <v/>
+        <v>agroecology, regenerative agriculture, rainfed conditions, small farms, food systems, diets, activism, choices</v>
       </c>
     </row>
     <row r="131" xml:space="preserve">
@@ -12136,13 +12136,13 @@
 Potentially replicable across other smallholder-dominated regions in SSA</v>
       </c>
       <c r="T131" t="str">
-        <v/>
+        <v>10.1007/s10098-022-02272-7</v>
       </c>
       <c r="U131" t="str">
-        <v/>
+        <v>Models that enable the estimation of crop yields and greenhouse gas (GHG) emissions concurrently are still lacking. This study develops a biophysical modelling framework encompassing a farm typology, a crop model, and a farm-focused GHG calculator to assess productivity (crop yield) and GHG emissions of crop management practices concurrently. Using this modelling framework, the study developed cropping system scenarios based on the concept of conservation agriculture (CA) to identify and design cropping systems that deliver ecological intensification for different farm types. All farm types were found to be net sources of GHG with cropping system inefficiency across all farm types. However, the integration of CA-based practices independently and in combination into farm-type maize-based cropping systems showed significant potential in improving crop yields and lowering GHG emissions across all farm types.</v>
       </c>
       <c r="V131" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="132" xml:space="preserve">
